--- a/TejToolAPI/tables/columns_group.xlsx
+++ b/TejToolAPI/tables/columns_group.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2022040601\Desktop\TEJ_TOOL_API\TejToolAPI\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1591689-CE71-4841-A92F-8DB90961812D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55CA39B-EF57-407A-AD08-61103599BF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,8 +24,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">API!$A$1:$B$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">table_columns!$C$1:$D$661</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">transfer_language!$A$1:$E$672</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">table_columns!$C$1:$D$686</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">transfer_language!$A$1:$E$697</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5122" uniqueCount="2075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5404" uniqueCount="2150">
   <si>
     <t>TABLE_NAMES</t>
   </si>
@@ -6455,6 +6455,233 @@
   </si>
   <si>
     <t>eng_name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a0112</t>
+  </si>
+  <si>
+    <t>現金及約當現金</t>
+  </si>
+  <si>
+    <t>a0130</t>
+  </si>
+  <si>
+    <t>應收帳款及票據</t>
+  </si>
+  <si>
+    <t>a0160</t>
+  </si>
+  <si>
+    <t>其他應收款</t>
+  </si>
+  <si>
+    <t>a0170</t>
+  </si>
+  <si>
+    <t>存貨</t>
+  </si>
+  <si>
+    <t>a0180</t>
+  </si>
+  <si>
+    <t>預付費用及預付款</t>
+  </si>
+  <si>
+    <t>a0400</t>
+  </si>
+  <si>
+    <t>不動產廠房及設備</t>
+  </si>
+  <si>
+    <t>a0820</t>
+  </si>
+  <si>
+    <t>商譽及無形資產合計</t>
+  </si>
+  <si>
+    <t>a118e</t>
+  </si>
+  <si>
+    <t>合約負債－流動</t>
+  </si>
+  <si>
+    <t>a1130</t>
+  </si>
+  <si>
+    <t>應付帳款及票據</t>
+  </si>
+  <si>
+    <t>a1190</t>
+  </si>
+  <si>
+    <t>其他應付款</t>
+  </si>
+  <si>
+    <t>a156p</t>
+  </si>
+  <si>
+    <t>合約負債-非流動</t>
+  </si>
+  <si>
+    <t>a2110</t>
+  </si>
+  <si>
+    <t>普通股股本</t>
+  </si>
+  <si>
+    <t>a2120</t>
+  </si>
+  <si>
+    <t>特別股股本</t>
+  </si>
+  <si>
+    <t>a211e</t>
+  </si>
+  <si>
+    <t>股本</t>
+  </si>
+  <si>
+    <t>a2310</t>
+  </si>
+  <si>
+    <t>資本公積合計</t>
+  </si>
+  <si>
+    <t>a2341</t>
+  </si>
+  <si>
+    <t>保留盈餘</t>
+  </si>
+  <si>
+    <t>a2480</t>
+  </si>
+  <si>
+    <t>其他權益</t>
+  </si>
+  <si>
+    <t>a2400</t>
+  </si>
+  <si>
+    <t>庫藏股票帳面值</t>
+  </si>
+  <si>
+    <t>a3352</t>
+  </si>
+  <si>
+    <t>推銷費用</t>
+  </si>
+  <si>
+    <t>a3355</t>
+  </si>
+  <si>
+    <t>管理費用</t>
+  </si>
+  <si>
+    <t>a3356</t>
+  </si>
+  <si>
+    <t>研究發展費</t>
+  </si>
+  <si>
+    <t>a3410</t>
+  </si>
+  <si>
+    <t>利息收入</t>
+  </si>
+  <si>
+    <t>a7211</t>
+  </si>
+  <si>
+    <t>折舊-CFO</t>
+  </si>
+  <si>
+    <t>a7212</t>
+  </si>
+  <si>
+    <t>a7324</t>
+  </si>
+  <si>
+    <t>購置不動產廠房設備(含預付)-CFI</t>
+  </si>
+  <si>
+    <t>Share_Capital</t>
+  </si>
+  <si>
+    <t>Accounts_And_Notes_Receivable</t>
+  </si>
+  <si>
+    <t>Other_Receivable</t>
+  </si>
+  <si>
+    <t>Total_Inventories</t>
+  </si>
+  <si>
+    <t>Total_Prepayments</t>
+  </si>
+  <si>
+    <t>Total_Property_Plant_And_Equipment</t>
+  </si>
+  <si>
+    <t>Goodwill_And_Intangible_Assets</t>
+  </si>
+  <si>
+    <t>Current_Contract_Liabilities</t>
+  </si>
+  <si>
+    <t>Accounts_And_Notes_Payable</t>
+  </si>
+  <si>
+    <t>Other_Payable</t>
+  </si>
+  <si>
+    <t>Noncurrent_Contract_Liabilities</t>
+  </si>
+  <si>
+    <t>Ordinary_Share</t>
+  </si>
+  <si>
+    <t>Preference_Share</t>
+  </si>
+  <si>
+    <t>Total_Capital_Surplus</t>
+  </si>
+  <si>
+    <t>Total_Retained_Earnings</t>
+  </si>
+  <si>
+    <t>Total_Other_Equity_Interest</t>
+  </si>
+  <si>
+    <t>Treasury_Shares</t>
+  </si>
+  <si>
+    <t>Total_Selling_Expenses</t>
+  </si>
+  <si>
+    <t>Total_Administrative_Expenses</t>
+  </si>
+  <si>
+    <t>Total_R_And_D_Expenses</t>
+  </si>
+  <si>
+    <t>Other_Income_Interest_Income</t>
+  </si>
+  <si>
+    <t>Depreciation_Expense_CFO</t>
+  </si>
+  <si>
+    <t>Amortization_Expense_CFO</t>
+  </si>
+  <si>
+    <t>Purchase_Of_Fixed_Assets_CFI</t>
+  </si>
+  <si>
+    <t>Total_Cash_And_Cash_Equivalents</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攤提－CFO</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6819,7 +7046,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C666"/>
+  <dimension ref="A1:C691"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.125" bestFit="1" customWidth="1"/>
@@ -12845,285 +13072,285 @@
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B548" t="s">
-        <v>155</v>
+        <v>2075</v>
       </c>
       <c r="C548" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B549" t="s">
-        <v>156</v>
+        <v>2077</v>
       </c>
       <c r="C549" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B550" t="s">
-        <v>151</v>
+        <v>2079</v>
       </c>
       <c r="C550" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B551" t="s">
-        <v>152</v>
+        <v>2081</v>
       </c>
       <c r="C551" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B552" t="s">
-        <v>153</v>
+        <v>2083</v>
       </c>
       <c r="C552" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B553" t="s">
-        <v>154</v>
+        <v>2085</v>
       </c>
       <c r="C553" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B554" t="s">
-        <v>157</v>
+        <v>2087</v>
       </c>
       <c r="C554" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B555" t="s">
-        <v>158</v>
+        <v>2089</v>
       </c>
       <c r="C555" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B556" t="s">
-        <v>159</v>
+        <v>2091</v>
       </c>
       <c r="C556" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B557" t="s">
-        <v>160</v>
+        <v>2093</v>
       </c>
       <c r="C557" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B558" t="s">
-        <v>161</v>
+        <v>2095</v>
       </c>
       <c r="C558" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B559" t="s">
-        <v>188</v>
+        <v>2097</v>
       </c>
       <c r="C559" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B560" t="s">
-        <v>189</v>
+        <v>2099</v>
       </c>
       <c r="C560" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B561" t="s">
-        <v>164</v>
+        <v>2101</v>
       </c>
       <c r="C561" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B562" t="s">
-        <v>165</v>
+        <v>2103</v>
       </c>
       <c r="C562" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B563" t="s">
-        <v>166</v>
+        <v>2105</v>
       </c>
       <c r="C563" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B564" t="s">
-        <v>167</v>
+        <v>2107</v>
       </c>
       <c r="C564" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B565" t="s">
-        <v>168</v>
+        <v>2109</v>
       </c>
       <c r="C565" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B566" t="s">
-        <v>1778</v>
+        <v>2111</v>
       </c>
       <c r="C566" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B567" t="s">
-        <v>1774</v>
+        <v>2113</v>
       </c>
       <c r="C567" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B568" t="s">
-        <v>1773</v>
+        <v>2115</v>
       </c>
       <c r="C568" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B569" t="s">
-        <v>1772</v>
+        <v>2117</v>
       </c>
       <c r="C569" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B570" t="s">
-        <v>1780</v>
+        <v>2119</v>
       </c>
       <c r="C570" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B571" t="s">
-        <v>1777</v>
+        <v>2121</v>
       </c>
       <c r="C571" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B572" t="s">
-        <v>1776</v>
+        <v>2122</v>
       </c>
       <c r="C572" t="s">
-        <v>1869</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B573" t="s">
-        <v>1775</v>
+        <v>155</v>
       </c>
       <c r="C573" t="s">
         <v>1869</v>
@@ -13131,10 +13358,10 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B574" t="s">
-        <v>1779</v>
+        <v>156</v>
       </c>
       <c r="C574" t="s">
         <v>1869</v>
@@ -13142,10 +13369,10 @@
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B575" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="C575" t="s">
         <v>1869</v>
@@ -13153,10 +13380,10 @@
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B576" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="C576" t="s">
         <v>1869</v>
@@ -13164,10 +13391,10 @@
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B577" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="C577" t="s">
         <v>1869</v>
@@ -13175,10 +13402,10 @@
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B578" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="C578" t="s">
         <v>1869</v>
@@ -13186,10 +13413,10 @@
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B579" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="C579" t="s">
         <v>1869</v>
@@ -13197,10 +13424,10 @@
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B580" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="C580" t="s">
         <v>1869</v>
@@ -13208,10 +13435,10 @@
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B581" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="C581" t="s">
         <v>1869</v>
@@ -13219,10 +13446,10 @@
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B582" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C582" t="s">
         <v>1869</v>
@@ -13230,10 +13457,10 @@
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B583" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="C583" t="s">
         <v>1869</v>
@@ -13241,10 +13468,10 @@
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B584" t="s">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="C584" t="s">
         <v>1869</v>
@@ -13252,10 +13479,10 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B585" t="s">
-        <v>1770</v>
+        <v>189</v>
       </c>
       <c r="C585" t="s">
         <v>1869</v>
@@ -13263,10 +13490,10 @@
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B586" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="C586" t="s">
         <v>1869</v>
@@ -13274,10 +13501,10 @@
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B587" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C587" t="s">
         <v>1869</v>
@@ -13285,10 +13512,10 @@
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B588" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="C588" t="s">
         <v>1869</v>
@@ -13296,10 +13523,10 @@
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B589" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="C589" t="s">
         <v>1869</v>
@@ -13307,10 +13534,10 @@
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B590" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="C590" t="s">
         <v>1869</v>
@@ -13321,7 +13548,7 @@
         <v>128</v>
       </c>
       <c r="B591" t="s">
-        <v>148</v>
+        <v>1778</v>
       </c>
       <c r="C591" t="s">
         <v>1869</v>
@@ -13332,7 +13559,7 @@
         <v>128</v>
       </c>
       <c r="B592" t="s">
-        <v>1781</v>
+        <v>1774</v>
       </c>
       <c r="C592" t="s">
         <v>1869</v>
@@ -13343,7 +13570,7 @@
         <v>128</v>
       </c>
       <c r="B593" t="s">
-        <v>136</v>
+        <v>1773</v>
       </c>
       <c r="C593" t="s">
         <v>1869</v>
@@ -13354,7 +13581,7 @@
         <v>128</v>
       </c>
       <c r="B594" t="s">
-        <v>137</v>
+        <v>1772</v>
       </c>
       <c r="C594" t="s">
         <v>1869</v>
@@ -13365,7 +13592,7 @@
         <v>128</v>
       </c>
       <c r="B595" t="s">
-        <v>139</v>
+        <v>1780</v>
       </c>
       <c r="C595" t="s">
         <v>1869</v>
@@ -13376,7 +13603,7 @@
         <v>128</v>
       </c>
       <c r="B596" t="s">
-        <v>140</v>
+        <v>1777</v>
       </c>
       <c r="C596" t="s">
         <v>1869</v>
@@ -13384,10 +13611,10 @@
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B597" t="s">
-        <v>108</v>
+        <v>1776</v>
       </c>
       <c r="C597" t="s">
         <v>1869</v>
@@ -13395,10 +13622,10 @@
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B598" t="s">
-        <v>109</v>
+        <v>1775</v>
       </c>
       <c r="C598" t="s">
         <v>1869</v>
@@ -13406,10 +13633,10 @@
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B599" t="s">
-        <v>116</v>
+        <v>1779</v>
       </c>
       <c r="C599" t="s">
         <v>1869</v>
@@ -13417,10 +13644,10 @@
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B600" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C600" t="s">
         <v>1869</v>
@@ -13428,10 +13655,10 @@
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B601" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C601" t="s">
         <v>1869</v>
@@ -13439,10 +13666,10 @@
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B602" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C602" t="s">
         <v>1869</v>
@@ -13450,10 +13677,10 @@
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B603" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C603" t="s">
         <v>1869</v>
@@ -13461,10 +13688,10 @@
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B604" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="C604" t="s">
         <v>1869</v>
@@ -13472,10 +13699,10 @@
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B605" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="C605" t="s">
         <v>1869</v>
@@ -13483,10 +13710,10 @@
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B606" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C606" t="s">
         <v>1869</v>
@@ -13494,10 +13721,10 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B607" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="C607" t="s">
         <v>1869</v>
@@ -13505,10 +13732,10 @@
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B608" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="C608" t="s">
         <v>1869</v>
@@ -13516,10 +13743,10 @@
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B609" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="C609" t="s">
         <v>1869</v>
@@ -13527,10 +13754,10 @@
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B610" t="s">
-        <v>112</v>
+        <v>1770</v>
       </c>
       <c r="C610" t="s">
         <v>1869</v>
@@ -13538,10 +13765,10 @@
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B611" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="C611" t="s">
         <v>1869</v>
@@ -13549,10 +13776,10 @@
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B612" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="C612" t="s">
         <v>1869</v>
@@ -13560,10 +13787,10 @@
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B613" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="C613" t="s">
         <v>1869</v>
@@ -13571,10 +13798,10 @@
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B614" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="C614" t="s">
         <v>1869</v>
@@ -13582,10 +13809,10 @@
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B615" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="C615" t="s">
         <v>1869</v>
@@ -13593,10 +13820,10 @@
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B616" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="C616" t="s">
         <v>1869</v>
@@ -13604,10 +13831,10 @@
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="B617" t="s">
-        <v>5</v>
+        <v>1781</v>
       </c>
       <c r="C617" t="s">
         <v>1869</v>
@@ -13615,10 +13842,10 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>1807</v>
+        <v>128</v>
       </c>
       <c r="B618" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C618" t="s">
         <v>1869</v>
@@ -13626,10 +13853,10 @@
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="B619" t="s">
-        <v>9</v>
+        <v>137</v>
       </c>
       <c r="C619" t="s">
         <v>1869</v>
@@ -13637,10 +13864,10 @@
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="B620" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="C620" t="s">
         <v>1869</v>
@@ -13648,10 +13875,10 @@
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="B621" t="s">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="C621" t="s">
         <v>1869</v>
@@ -13659,10 +13886,10 @@
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B622" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="C622" t="s">
         <v>1869</v>
@@ -13670,10 +13897,10 @@
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B623" t="s">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="C623" t="s">
         <v>1869</v>
@@ -13681,10 +13908,10 @@
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B624" t="s">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="C624" t="s">
         <v>1869</v>
@@ -13692,10 +13919,10 @@
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B625" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="C625" t="s">
         <v>1869</v>
@@ -13703,10 +13930,10 @@
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B626" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="C626" t="s">
         <v>1869</v>
@@ -13714,10 +13941,10 @@
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B627" t="s">
-        <v>11</v>
+        <v>125</v>
       </c>
       <c r="C627" t="s">
         <v>1869</v>
@@ -13725,10 +13952,10 @@
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B628" t="s">
-        <v>1761</v>
+        <v>113</v>
       </c>
       <c r="C628" t="s">
         <v>1869</v>
@@ -13736,10 +13963,10 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B629" t="s">
-        <v>1749</v>
+        <v>110</v>
       </c>
       <c r="C629" t="s">
         <v>1869</v>
@@ -13747,10 +13974,10 @@
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B630" t="s">
-        <v>7</v>
+        <v>118</v>
       </c>
       <c r="C630" t="s">
         <v>1869</v>
@@ -13758,10 +13985,10 @@
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B631" t="s">
-        <v>1743</v>
+        <v>121</v>
       </c>
       <c r="C631" t="s">
         <v>1869</v>
@@ -13769,10 +13996,10 @@
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B632" t="s">
-        <v>1744</v>
+        <v>124</v>
       </c>
       <c r="C632" t="s">
         <v>1869</v>
@@ -13780,10 +14007,10 @@
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B633" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="C633" t="s">
         <v>1869</v>
@@ -13791,10 +14018,10 @@
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B634" t="s">
-        <v>1803</v>
+        <v>115</v>
       </c>
       <c r="C634" t="s">
         <v>1869</v>
@@ -13802,10 +14029,10 @@
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B635" t="s">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="C635" t="s">
         <v>1869</v>
@@ -13813,10 +14040,10 @@
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B636" t="s">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="C636" t="s">
         <v>1869</v>
@@ -13824,10 +14051,10 @@
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B637" t="s">
-        <v>1754</v>
+        <v>120</v>
       </c>
       <c r="C637" t="s">
         <v>1869</v>
@@ -13835,10 +14062,10 @@
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B638" t="s">
-        <v>1755</v>
+        <v>123</v>
       </c>
       <c r="C638" t="s">
         <v>1869</v>
@@ -13846,10 +14073,10 @@
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B639" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="C639" t="s">
         <v>1869</v>
@@ -13857,10 +14084,10 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="B640" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="C640" t="s">
         <v>1869</v>
@@ -13868,10 +14095,10 @@
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="B641" t="s">
-        <v>43</v>
+        <v>111</v>
       </c>
       <c r="C641" t="s">
         <v>1869</v>
@@ -13879,10 +14106,10 @@
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B642" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C642" t="s">
         <v>1869</v>
@@ -13890,10 +14117,10 @@
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>2</v>
+        <v>1807</v>
       </c>
       <c r="B643" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C643" t="s">
         <v>1869</v>
@@ -13901,10 +14128,10 @@
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B644" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C644" t="s">
         <v>1869</v>
@@ -13912,10 +14139,10 @@
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B645" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C645" t="s">
         <v>1869</v>
@@ -13923,10 +14150,10 @@
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B646" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="C646" t="s">
         <v>1869</v>
@@ -13934,10 +14161,10 @@
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B647" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C647" t="s">
         <v>1869</v>
@@ -13945,10 +14172,10 @@
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B648" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C648" t="s">
         <v>1869</v>
@@ -13956,10 +14183,10 @@
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B649" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C649" t="s">
         <v>1869</v>
@@ -13967,10 +14194,10 @@
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B650" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C650" t="s">
         <v>1869</v>
@@ -13978,10 +14205,10 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B651" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C651" t="s">
         <v>1869</v>
@@ -13989,10 +14216,10 @@
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B652" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C652" t="s">
         <v>1869</v>
@@ -14000,10 +14227,10 @@
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B653" t="s">
-        <v>36</v>
+        <v>1761</v>
       </c>
       <c r="C653" t="s">
         <v>1869</v>
@@ -14011,10 +14238,10 @@
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B654" t="s">
-        <v>37</v>
+        <v>1749</v>
       </c>
       <c r="C654" t="s">
         <v>1869</v>
@@ -14022,10 +14249,10 @@
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B655" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C655" t="s">
         <v>1869</v>
@@ -14033,10 +14260,10 @@
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B656" t="s">
-        <v>21</v>
+        <v>1743</v>
       </c>
       <c r="C656" t="s">
         <v>1869</v>
@@ -14044,10 +14271,10 @@
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B657" t="s">
-        <v>40</v>
+        <v>1744</v>
       </c>
       <c r="C657" t="s">
         <v>1869</v>
@@ -14055,10 +14282,10 @@
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B658" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C658" t="s">
         <v>1869</v>
@@ -14066,10 +14293,10 @@
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B659" t="s">
-        <v>39</v>
+        <v>1803</v>
       </c>
       <c r="C659" t="s">
         <v>1869</v>
@@ -14077,10 +14304,10 @@
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B660" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="C660" t="s">
         <v>1869</v>
@@ -14088,10 +14315,10 @@
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B661" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="C661" t="s">
         <v>1869</v>
@@ -14099,10 +14326,10 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B662" t="s">
-        <v>32</v>
+        <v>1754</v>
       </c>
       <c r="C662" t="s">
         <v>1869</v>
@@ -14110,10 +14337,10 @@
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B663" t="s">
-        <v>35</v>
+        <v>1755</v>
       </c>
       <c r="C663" t="s">
         <v>1869</v>
@@ -14121,10 +14348,10 @@
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B664" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C664" t="s">
         <v>1869</v>
@@ -14135,7 +14362,7 @@
         <v>2</v>
       </c>
       <c r="B665" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C665" t="s">
         <v>1869</v>
@@ -14146,14 +14373,289 @@
         <v>2</v>
       </c>
       <c r="B666" t="s">
+        <v>43</v>
+      </c>
+      <c r="C666" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A667" t="s">
+        <v>2</v>
+      </c>
+      <c r="B667" t="s">
+        <v>27</v>
+      </c>
+      <c r="C667" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A668" t="s">
+        <v>2</v>
+      </c>
+      <c r="B668" t="s">
+        <v>38</v>
+      </c>
+      <c r="C668" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A669" t="s">
+        <v>2</v>
+      </c>
+      <c r="B669" t="s">
+        <v>31</v>
+      </c>
+      <c r="C669" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A670" t="s">
+        <v>2</v>
+      </c>
+      <c r="B670" t="s">
+        <v>29</v>
+      </c>
+      <c r="C670" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A671" t="s">
+        <v>2</v>
+      </c>
+      <c r="B671" t="s">
+        <v>42</v>
+      </c>
+      <c r="C671" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A672" t="s">
+        <v>2</v>
+      </c>
+      <c r="B672" t="s">
+        <v>24</v>
+      </c>
+      <c r="C672" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A673" t="s">
+        <v>2</v>
+      </c>
+      <c r="B673" t="s">
+        <v>41</v>
+      </c>
+      <c r="C673" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A674" t="s">
+        <v>2</v>
+      </c>
+      <c r="B674" t="s">
+        <v>22</v>
+      </c>
+      <c r="C674" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A675" t="s">
+        <v>2</v>
+      </c>
+      <c r="B675" t="s">
+        <v>33</v>
+      </c>
+      <c r="C675" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A676" t="s">
+        <v>2</v>
+      </c>
+      <c r="B676" t="s">
+        <v>23</v>
+      </c>
+      <c r="C676" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A677" t="s">
+        <v>2</v>
+      </c>
+      <c r="B677" t="s">
+        <v>3</v>
+      </c>
+      <c r="C677" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A678" t="s">
+        <v>2</v>
+      </c>
+      <c r="B678" t="s">
+        <v>36</v>
+      </c>
+      <c r="C678" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A679" t="s">
+        <v>2</v>
+      </c>
+      <c r="B679" t="s">
+        <v>37</v>
+      </c>
+      <c r="C679" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A680" t="s">
+        <v>2</v>
+      </c>
+      <c r="B680" t="s">
+        <v>30</v>
+      </c>
+      <c r="C680" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A681" t="s">
+        <v>2</v>
+      </c>
+      <c r="B681" t="s">
+        <v>21</v>
+      </c>
+      <c r="C681" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A682" t="s">
+        <v>2</v>
+      </c>
+      <c r="B682" t="s">
+        <v>40</v>
+      </c>
+      <c r="C682" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A683" t="s">
+        <v>2</v>
+      </c>
+      <c r="B683" t="s">
+        <v>45</v>
+      </c>
+      <c r="C683" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A684" t="s">
+        <v>2</v>
+      </c>
+      <c r="B684" t="s">
+        <v>39</v>
+      </c>
+      <c r="C684" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A685" t="s">
+        <v>2</v>
+      </c>
+      <c r="B685" t="s">
+        <v>44</v>
+      </c>
+      <c r="C685" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A686" t="s">
+        <v>2</v>
+      </c>
+      <c r="B686" t="s">
+        <v>46</v>
+      </c>
+      <c r="C686" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A687" t="s">
+        <v>2</v>
+      </c>
+      <c r="B687" t="s">
+        <v>32</v>
+      </c>
+      <c r="C687" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A688" t="s">
+        <v>2</v>
+      </c>
+      <c r="B688" t="s">
+        <v>35</v>
+      </c>
+      <c r="C688" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A689" t="s">
+        <v>2</v>
+      </c>
+      <c r="B689" t="s">
+        <v>28</v>
+      </c>
+      <c r="C689" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A690" t="s">
+        <v>2</v>
+      </c>
+      <c r="B690" t="s">
+        <v>34</v>
+      </c>
+      <c r="C690" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A691" t="s">
+        <v>2</v>
+      </c>
+      <c r="B691" t="s">
         <v>26</v>
       </c>
-      <c r="C666" t="s">
+      <c r="C691" t="s">
         <v>1869</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B696">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B721">
     <sortCondition ref="A1"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14346,7 +14848,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E672"/>
+  <dimension ref="A1:E697"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.125" bestFit="1" customWidth="1"/>
@@ -21081,6 +21583,9 @@
       <c r="B468" t="s">
         <v>1918</v>
       </c>
+      <c r="C468" t="s">
+        <v>872</v>
+      </c>
       <c r="D468" t="s">
         <v>1919</v>
       </c>
@@ -21095,6 +21600,9 @@
       <c r="B469" t="s">
         <v>1920</v>
       </c>
+      <c r="C469" t="s">
+        <v>872</v>
+      </c>
       <c r="D469" t="s">
         <v>1921</v>
       </c>
@@ -21109,6 +21617,9 @@
       <c r="B470" t="s">
         <v>1922</v>
       </c>
+      <c r="C470" t="s">
+        <v>872</v>
+      </c>
       <c r="D470" t="s">
         <v>1923</v>
       </c>
@@ -21123,6 +21634,9 @@
       <c r="B471" t="s">
         <v>1924</v>
       </c>
+      <c r="C471" t="s">
+        <v>872</v>
+      </c>
       <c r="D471" t="s">
         <v>1925</v>
       </c>
@@ -21137,6 +21651,9 @@
       <c r="B472" t="s">
         <v>1926</v>
       </c>
+      <c r="C472" t="s">
+        <v>872</v>
+      </c>
       <c r="D472" t="s">
         <v>1927</v>
       </c>
@@ -21151,6 +21668,9 @@
       <c r="B473" t="s">
         <v>1928</v>
       </c>
+      <c r="C473" t="s">
+        <v>872</v>
+      </c>
       <c r="D473" t="s">
         <v>912</v>
       </c>
@@ -21165,6 +21685,9 @@
       <c r="B474" t="s">
         <v>1929</v>
       </c>
+      <c r="C474" t="s">
+        <v>872</v>
+      </c>
       <c r="D474" t="s">
         <v>1930</v>
       </c>
@@ -21179,6 +21702,9 @@
       <c r="B475" t="s">
         <v>1931</v>
       </c>
+      <c r="C475" t="s">
+        <v>872</v>
+      </c>
       <c r="D475" t="s">
         <v>907</v>
       </c>
@@ -21193,6 +21719,9 @@
       <c r="B476" t="s">
         <v>1932</v>
       </c>
+      <c r="C476" t="s">
+        <v>872</v>
+      </c>
       <c r="D476" t="s">
         <v>1933</v>
       </c>
@@ -21207,6 +21736,9 @@
       <c r="B477" t="s">
         <v>1934</v>
       </c>
+      <c r="C477" t="s">
+        <v>872</v>
+      </c>
       <c r="D477" t="s">
         <v>1935</v>
       </c>
@@ -21221,6 +21753,9 @@
       <c r="B478" t="s">
         <v>1936</v>
       </c>
+      <c r="C478" t="s">
+        <v>872</v>
+      </c>
       <c r="D478" t="s">
         <v>916</v>
       </c>
@@ -21235,6 +21770,9 @@
       <c r="B479" t="s">
         <v>1937</v>
       </c>
+      <c r="C479" t="s">
+        <v>872</v>
+      </c>
       <c r="D479" t="s">
         <v>1938</v>
       </c>
@@ -21249,6 +21787,9 @@
       <c r="B480" t="s">
         <v>1939</v>
       </c>
+      <c r="C480" t="s">
+        <v>872</v>
+      </c>
       <c r="D480" t="s">
         <v>929</v>
       </c>
@@ -21263,6 +21804,9 @@
       <c r="B481" t="s">
         <v>1940</v>
       </c>
+      <c r="C481" t="s">
+        <v>872</v>
+      </c>
       <c r="D481" t="s">
         <v>918</v>
       </c>
@@ -21277,6 +21821,9 @@
       <c r="B482" t="s">
         <v>1941</v>
       </c>
+      <c r="C482" t="s">
+        <v>872</v>
+      </c>
       <c r="D482" t="s">
         <v>931</v>
       </c>
@@ -21291,6 +21838,9 @@
       <c r="B483" t="s">
         <v>1942</v>
       </c>
+      <c r="C483" t="s">
+        <v>872</v>
+      </c>
       <c r="D483" t="s">
         <v>1943</v>
       </c>
@@ -21305,6 +21855,9 @@
       <c r="B484" t="s">
         <v>1944</v>
       </c>
+      <c r="C484" t="s">
+        <v>872</v>
+      </c>
       <c r="D484" t="s">
         <v>1945</v>
       </c>
@@ -21319,6 +21872,9 @@
       <c r="B485" t="s">
         <v>1946</v>
       </c>
+      <c r="C485" t="s">
+        <v>872</v>
+      </c>
       <c r="D485" t="s">
         <v>921</v>
       </c>
@@ -21333,6 +21889,9 @@
       <c r="B486" t="s">
         <v>1947</v>
       </c>
+      <c r="C486" t="s">
+        <v>872</v>
+      </c>
       <c r="D486" t="s">
         <v>1948</v>
       </c>
@@ -21347,6 +21906,9 @@
       <c r="B487" t="s">
         <v>1949</v>
       </c>
+      <c r="C487" t="s">
+        <v>872</v>
+      </c>
       <c r="D487" t="s">
         <v>1950</v>
       </c>
@@ -21361,6 +21923,9 @@
       <c r="B488" t="s">
         <v>1951</v>
       </c>
+      <c r="C488" t="s">
+        <v>872</v>
+      </c>
       <c r="D488" t="s">
         <v>923</v>
       </c>
@@ -21375,6 +21940,9 @@
       <c r="B489" t="s">
         <v>1952</v>
       </c>
+      <c r="C489" t="s">
+        <v>872</v>
+      </c>
       <c r="D489" t="s">
         <v>925</v>
       </c>
@@ -21389,6 +21957,9 @@
       <c r="B490" t="s">
         <v>2064</v>
       </c>
+      <c r="C490" t="s">
+        <v>872</v>
+      </c>
       <c r="D490" t="s">
         <v>927</v>
       </c>
@@ -21403,6 +21974,9 @@
       <c r="B491" t="s">
         <v>1953</v>
       </c>
+      <c r="C491" t="s">
+        <v>872</v>
+      </c>
       <c r="D491" t="s">
         <v>934</v>
       </c>
@@ -21417,6 +21991,9 @@
       <c r="B492" t="s">
         <v>1954</v>
       </c>
+      <c r="C492" t="s">
+        <v>872</v>
+      </c>
       <c r="D492" t="s">
         <v>2010</v>
       </c>
@@ -21431,6 +22008,9 @@
       <c r="B493" t="s">
         <v>1955</v>
       </c>
+      <c r="C493" t="s">
+        <v>872</v>
+      </c>
       <c r="D493" t="s">
         <v>1956</v>
       </c>
@@ -21445,6 +22025,9 @@
       <c r="B494" t="s">
         <v>1957</v>
       </c>
+      <c r="C494" t="s">
+        <v>872</v>
+      </c>
       <c r="D494" t="s">
         <v>1958</v>
       </c>
@@ -21459,6 +22042,9 @@
       <c r="B495" t="s">
         <v>1959</v>
       </c>
+      <c r="C495" t="s">
+        <v>872</v>
+      </c>
       <c r="D495" t="s">
         <v>2009</v>
       </c>
@@ -21473,6 +22059,9 @@
       <c r="B496" t="s">
         <v>1960</v>
       </c>
+      <c r="C496" t="s">
+        <v>872</v>
+      </c>
       <c r="D496" t="s">
         <v>1961</v>
       </c>
@@ -21487,6 +22076,9 @@
       <c r="B497" t="s">
         <v>1962</v>
       </c>
+      <c r="C497" t="s">
+        <v>872</v>
+      </c>
       <c r="D497" t="s">
         <v>933</v>
       </c>
@@ -21501,6 +22093,9 @@
       <c r="B498" t="s">
         <v>1963</v>
       </c>
+      <c r="C498" t="s">
+        <v>872</v>
+      </c>
       <c r="D498" t="s">
         <v>1964</v>
       </c>
@@ -21515,6 +22110,9 @@
       <c r="B499" t="s">
         <v>1965</v>
       </c>
+      <c r="C499" t="s">
+        <v>872</v>
+      </c>
       <c r="D499" t="s">
         <v>1966</v>
       </c>
@@ -21529,6 +22127,9 @@
       <c r="B500" t="s">
         <v>1967</v>
       </c>
+      <c r="C500" t="s">
+        <v>872</v>
+      </c>
       <c r="D500" t="s">
         <v>1968</v>
       </c>
@@ -21543,6 +22144,9 @@
       <c r="B501" t="s">
         <v>1969</v>
       </c>
+      <c r="C501" t="s">
+        <v>872</v>
+      </c>
       <c r="D501" t="s">
         <v>1970</v>
       </c>
@@ -21557,6 +22161,9 @@
       <c r="B502" t="s">
         <v>1971</v>
       </c>
+      <c r="C502" t="s">
+        <v>872</v>
+      </c>
       <c r="D502" t="s">
         <v>1972</v>
       </c>
@@ -21571,6 +22178,9 @@
       <c r="B503" t="s">
         <v>1973</v>
       </c>
+      <c r="C503" t="s">
+        <v>872</v>
+      </c>
       <c r="D503" t="s">
         <v>2012</v>
       </c>
@@ -21585,6 +22195,9 @@
       <c r="B504" t="s">
         <v>1974</v>
       </c>
+      <c r="C504" t="s">
+        <v>872</v>
+      </c>
       <c r="D504" t="s">
         <v>2011</v>
       </c>
@@ -21599,6 +22212,9 @@
       <c r="B505" t="s">
         <v>1975</v>
       </c>
+      <c r="C505" t="s">
+        <v>872</v>
+      </c>
       <c r="D505" t="s">
         <v>1976</v>
       </c>
@@ -21613,6 +22229,9 @@
       <c r="B506" t="s">
         <v>158</v>
       </c>
+      <c r="C506" t="s">
+        <v>872</v>
+      </c>
       <c r="D506" t="s">
         <v>935</v>
       </c>
@@ -21627,6 +22246,9 @@
       <c r="B507" t="s">
         <v>159</v>
       </c>
+      <c r="C507" t="s">
+        <v>872</v>
+      </c>
       <c r="D507" t="s">
         <v>937</v>
       </c>
@@ -21641,6 +22263,9 @@
       <c r="B508" t="s">
         <v>160</v>
       </c>
+      <c r="C508" t="s">
+        <v>872</v>
+      </c>
       <c r="D508" t="s">
         <v>939</v>
       </c>
@@ -21655,6 +22280,9 @@
       <c r="B509" t="s">
         <v>161</v>
       </c>
+      <c r="C509" t="s">
+        <v>872</v>
+      </c>
       <c r="D509" t="s">
         <v>941</v>
       </c>
@@ -21669,6 +22297,9 @@
       <c r="B510" t="s">
         <v>163</v>
       </c>
+      <c r="C510" t="s">
+        <v>872</v>
+      </c>
       <c r="D510" t="s">
         <v>1977</v>
       </c>
@@ -21683,6 +22314,9 @@
       <c r="B511" t="s">
         <v>162</v>
       </c>
+      <c r="C511" t="s">
+        <v>872</v>
+      </c>
       <c r="D511" t="s">
         <v>943</v>
       </c>
@@ -21697,6 +22331,9 @@
       <c r="B512" t="s">
         <v>1978</v>
       </c>
+      <c r="C512" t="s">
+        <v>872</v>
+      </c>
       <c r="D512" t="s">
         <v>1979</v>
       </c>
@@ -21711,6 +22348,9 @@
       <c r="B513" t="s">
         <v>173</v>
       </c>
+      <c r="C513" t="s">
+        <v>872</v>
+      </c>
       <c r="D513" t="s">
         <v>959</v>
       </c>
@@ -21725,6 +22365,9 @@
       <c r="B514" t="s">
         <v>185</v>
       </c>
+      <c r="C514" t="s">
+        <v>872</v>
+      </c>
       <c r="D514" t="s">
         <v>2013</v>
       </c>
@@ -21739,6 +22382,9 @@
       <c r="B515" t="s">
         <v>186</v>
       </c>
+      <c r="C515" t="s">
+        <v>872</v>
+      </c>
       <c r="D515" t="s">
         <v>1980</v>
       </c>
@@ -21753,6 +22399,9 @@
       <c r="B516" t="s">
         <v>187</v>
       </c>
+      <c r="C516" t="s">
+        <v>872</v>
+      </c>
       <c r="D516" t="s">
         <v>970</v>
       </c>
@@ -21767,6 +22416,9 @@
       <c r="B517" t="s">
         <v>188</v>
       </c>
+      <c r="C517" t="s">
+        <v>872</v>
+      </c>
       <c r="D517" t="s">
         <v>972</v>
       </c>
@@ -21781,6 +22433,9 @@
       <c r="B518" t="s">
         <v>164</v>
       </c>
+      <c r="C518" t="s">
+        <v>872</v>
+      </c>
       <c r="D518" t="s">
         <v>945</v>
       </c>
@@ -21795,6 +22450,9 @@
       <c r="B519" t="s">
         <v>165</v>
       </c>
+      <c r="C519" t="s">
+        <v>872</v>
+      </c>
       <c r="D519" t="s">
         <v>947</v>
       </c>
@@ -21809,6 +22467,9 @@
       <c r="B520" t="s">
         <v>166</v>
       </c>
+      <c r="C520" t="s">
+        <v>872</v>
+      </c>
       <c r="D520" t="s">
         <v>949</v>
       </c>
@@ -21823,6 +22484,9 @@
       <c r="B521" t="s">
         <v>167</v>
       </c>
+      <c r="C521" t="s">
+        <v>872</v>
+      </c>
       <c r="D521" t="s">
         <v>951</v>
       </c>
@@ -21837,6 +22501,9 @@
       <c r="B522" t="s">
         <v>168</v>
       </c>
+      <c r="C522" t="s">
+        <v>872</v>
+      </c>
       <c r="D522" t="s">
         <v>953</v>
       </c>
@@ -21851,6 +22518,9 @@
       <c r="B523" t="s">
         <v>169</v>
       </c>
+      <c r="C523" t="s">
+        <v>872</v>
+      </c>
       <c r="D523" t="s">
         <v>1981</v>
       </c>
@@ -21865,6 +22535,9 @@
       <c r="B524" t="s">
         <v>170</v>
       </c>
+      <c r="C524" t="s">
+        <v>872</v>
+      </c>
       <c r="D524" t="s">
         <v>955</v>
       </c>
@@ -21879,6 +22552,9 @@
       <c r="B525" t="s">
         <v>172</v>
       </c>
+      <c r="C525" t="s">
+        <v>872</v>
+      </c>
       <c r="D525" t="s">
         <v>957</v>
       </c>
@@ -21893,6 +22569,9 @@
       <c r="B526" t="s">
         <v>171</v>
       </c>
+      <c r="C526" t="s">
+        <v>872</v>
+      </c>
       <c r="D526" t="s">
         <v>956</v>
       </c>
@@ -21907,6 +22586,9 @@
       <c r="B527" t="s">
         <v>174</v>
       </c>
+      <c r="C527" t="s">
+        <v>872</v>
+      </c>
       <c r="D527" t="s">
         <v>960</v>
       </c>
@@ -21921,6 +22603,9 @@
       <c r="B528" t="s">
         <v>150</v>
       </c>
+      <c r="C528" t="s">
+        <v>872</v>
+      </c>
       <c r="D528" t="s">
         <v>915</v>
       </c>
@@ -21935,6 +22620,9 @@
       <c r="B529" t="s">
         <v>176</v>
       </c>
+      <c r="C529" t="s">
+        <v>872</v>
+      </c>
       <c r="D529" t="s">
         <v>964</v>
       </c>
@@ -21949,6 +22637,9 @@
       <c r="B530" t="s">
         <v>175</v>
       </c>
+      <c r="C530" t="s">
+        <v>872</v>
+      </c>
       <c r="D530" t="s">
         <v>962</v>
       </c>
@@ -21963,6 +22654,9 @@
       <c r="B531" t="s">
         <v>177</v>
       </c>
+      <c r="C531" t="s">
+        <v>872</v>
+      </c>
       <c r="D531" t="s">
         <v>1982</v>
       </c>
@@ -21977,6 +22671,9 @@
       <c r="B532" t="s">
         <v>179</v>
       </c>
+      <c r="C532" t="s">
+        <v>872</v>
+      </c>
       <c r="D532" t="s">
         <v>1983</v>
       </c>
@@ -21991,6 +22688,9 @@
       <c r="B533" t="s">
         <v>182</v>
       </c>
+      <c r="C533" t="s">
+        <v>872</v>
+      </c>
       <c r="D533" t="s">
         <v>1984</v>
       </c>
@@ -22005,6 +22705,9 @@
       <c r="B534" t="s">
         <v>178</v>
       </c>
+      <c r="C534" t="s">
+        <v>872</v>
+      </c>
       <c r="D534" t="s">
         <v>2014</v>
       </c>
@@ -22019,6 +22722,9 @@
       <c r="B535" t="s">
         <v>184</v>
       </c>
+      <c r="C535" t="s">
+        <v>872</v>
+      </c>
       <c r="D535" t="s">
         <v>1985</v>
       </c>
@@ -22033,6 +22739,9 @@
       <c r="B536" t="s">
         <v>181</v>
       </c>
+      <c r="C536" t="s">
+        <v>872</v>
+      </c>
       <c r="D536" t="s">
         <v>1986</v>
       </c>
@@ -22047,6 +22756,9 @@
       <c r="B537" t="s">
         <v>180</v>
       </c>
+      <c r="C537" t="s">
+        <v>872</v>
+      </c>
       <c r="D537" t="s">
         <v>2015</v>
       </c>
@@ -22061,6 +22773,9 @@
       <c r="B538" t="s">
         <v>183</v>
       </c>
+      <c r="C538" t="s">
+        <v>872</v>
+      </c>
       <c r="D538" t="s">
         <v>1987</v>
       </c>
@@ -22075,6 +22790,9 @@
       <c r="B539" t="s">
         <v>1988</v>
       </c>
+      <c r="C539" t="s">
+        <v>872</v>
+      </c>
       <c r="D539" t="s">
         <v>1989</v>
       </c>
@@ -22089,6 +22807,9 @@
       <c r="B540" t="s">
         <v>1990</v>
       </c>
+      <c r="C540" t="s">
+        <v>872</v>
+      </c>
       <c r="D540" t="s">
         <v>1991</v>
       </c>
@@ -22103,6 +22824,9 @@
       <c r="B541" t="s">
         <v>1992</v>
       </c>
+      <c r="C541" t="s">
+        <v>872</v>
+      </c>
       <c r="D541" t="s">
         <v>1993</v>
       </c>
@@ -22117,6 +22841,9 @@
       <c r="B542" t="s">
         <v>1994</v>
       </c>
+      <c r="C542" t="s">
+        <v>872</v>
+      </c>
       <c r="D542" t="s">
         <v>1995</v>
       </c>
@@ -22131,6 +22858,9 @@
       <c r="B543" t="s">
         <v>1996</v>
       </c>
+      <c r="C543" t="s">
+        <v>872</v>
+      </c>
       <c r="D543" t="s">
         <v>1997</v>
       </c>
@@ -22145,6 +22875,9 @@
       <c r="B544" t="s">
         <v>1998</v>
       </c>
+      <c r="C544" t="s">
+        <v>872</v>
+      </c>
       <c r="D544" t="s">
         <v>1999</v>
       </c>
@@ -22159,6 +22892,9 @@
       <c r="B545" t="s">
         <v>2000</v>
       </c>
+      <c r="C545" t="s">
+        <v>872</v>
+      </c>
       <c r="D545" t="s">
         <v>2001</v>
       </c>
@@ -22173,6 +22909,9 @@
       <c r="B546" t="s">
         <v>2002</v>
       </c>
+      <c r="C546" t="s">
+        <v>872</v>
+      </c>
       <c r="D546" t="s">
         <v>2003</v>
       </c>
@@ -22187,6 +22926,9 @@
       <c r="B547" t="s">
         <v>2004</v>
       </c>
+      <c r="C547" t="s">
+        <v>872</v>
+      </c>
       <c r="D547" t="s">
         <v>2005</v>
       </c>
@@ -22201,6 +22943,9 @@
       <c r="B548" t="s">
         <v>2006</v>
       </c>
+      <c r="C548" t="s">
+        <v>872</v>
+      </c>
       <c r="D548" t="s">
         <v>2007</v>
       </c>
@@ -22215,6 +22960,9 @@
       <c r="B549" t="s">
         <v>2008</v>
       </c>
+      <c r="C549" t="s">
+        <v>872</v>
+      </c>
       <c r="D549" t="s">
         <v>2016</v>
       </c>
@@ -22224,764 +22972,767 @@
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B550" t="s">
-        <v>594</v>
+        <v>2075</v>
       </c>
       <c r="C550" t="s">
-        <v>595</v>
+        <v>872</v>
       </c>
       <c r="D550" t="s">
-        <v>596</v>
+        <v>2076</v>
       </c>
       <c r="E550" t="s">
-        <v>594</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B551" t="s">
-        <v>594</v>
+        <v>2077</v>
       </c>
       <c r="C551" t="s">
-        <v>595</v>
+        <v>872</v>
       </c>
       <c r="D551" t="s">
-        <v>596</v>
+        <v>2078</v>
       </c>
       <c r="E551" t="s">
-        <v>594</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B552" t="s">
-        <v>2067</v>
+        <v>2079</v>
       </c>
       <c r="C552" t="s">
         <v>872</v>
       </c>
       <c r="D552" t="s">
-        <v>916</v>
+        <v>2080</v>
       </c>
       <c r="E552" t="s">
-        <v>917</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B553" t="s">
-        <v>157</v>
+        <v>2081</v>
       </c>
       <c r="C553" t="s">
         <v>872</v>
       </c>
       <c r="D553" t="s">
-        <v>931</v>
+        <v>2082</v>
       </c>
       <c r="E553" t="s">
-        <v>932</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B554" t="s">
-        <v>152</v>
+        <v>2083</v>
       </c>
       <c r="C554" t="s">
         <v>872</v>
       </c>
       <c r="D554" t="s">
-        <v>921</v>
+        <v>2084</v>
       </c>
       <c r="E554" t="s">
-        <v>922</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B555" t="s">
-        <v>153</v>
+        <v>2085</v>
       </c>
       <c r="C555" t="s">
         <v>872</v>
       </c>
       <c r="D555" t="s">
-        <v>923</v>
+        <v>2086</v>
       </c>
       <c r="E555" t="s">
-        <v>924</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B556" t="s">
-        <v>154</v>
+        <v>2087</v>
       </c>
       <c r="C556" t="s">
         <v>872</v>
       </c>
       <c r="D556" t="s">
-        <v>925</v>
+        <v>2088</v>
       </c>
       <c r="E556" t="s">
-        <v>926</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B557" t="s">
-        <v>155</v>
+        <v>2089</v>
       </c>
       <c r="C557" t="s">
         <v>872</v>
       </c>
       <c r="D557" t="s">
-        <v>2066</v>
+        <v>2090</v>
       </c>
       <c r="E557" t="s">
-        <v>928</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B558" t="s">
-        <v>156</v>
+        <v>2091</v>
       </c>
       <c r="C558" t="s">
         <v>872</v>
       </c>
       <c r="D558" t="s">
-        <v>929</v>
+        <v>2092</v>
       </c>
       <c r="E558" t="s">
-        <v>930</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B559" t="s">
-        <v>158</v>
+        <v>2093</v>
       </c>
       <c r="C559" t="s">
         <v>872</v>
       </c>
       <c r="D559" t="s">
-        <v>935</v>
+        <v>2094</v>
       </c>
       <c r="E559" t="s">
-        <v>936</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B560" t="s">
-        <v>159</v>
+        <v>2095</v>
       </c>
       <c r="C560" t="s">
         <v>872</v>
       </c>
       <c r="D560" t="s">
-        <v>937</v>
+        <v>2096</v>
       </c>
       <c r="E560" t="s">
-        <v>938</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B561" t="s">
-        <v>160</v>
+        <v>2097</v>
       </c>
       <c r="C561" t="s">
         <v>872</v>
       </c>
       <c r="D561" t="s">
-        <v>939</v>
+        <v>2098</v>
       </c>
       <c r="E561" t="s">
-        <v>940</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B562" t="s">
-        <v>161</v>
+        <v>2099</v>
       </c>
       <c r="C562" t="s">
         <v>872</v>
       </c>
       <c r="D562" t="s">
-        <v>941</v>
+        <v>2100</v>
       </c>
       <c r="E562" t="s">
-        <v>942</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B563" t="s">
-        <v>164</v>
+        <v>2101</v>
       </c>
       <c r="C563" t="s">
         <v>872</v>
       </c>
       <c r="D563" t="s">
-        <v>945</v>
+        <v>2102</v>
       </c>
       <c r="E563" t="s">
-        <v>946</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B564" t="s">
-        <v>165</v>
+        <v>2103</v>
       </c>
       <c r="C564" t="s">
         <v>872</v>
       </c>
       <c r="D564" t="s">
-        <v>947</v>
+        <v>2104</v>
       </c>
       <c r="E564" t="s">
-        <v>948</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B565" t="s">
-        <v>166</v>
+        <v>2105</v>
       </c>
       <c r="C565" t="s">
         <v>872</v>
       </c>
       <c r="D565" t="s">
-        <v>949</v>
+        <v>2106</v>
       </c>
       <c r="E565" t="s">
-        <v>950</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B566" t="s">
-        <v>167</v>
+        <v>2107</v>
       </c>
       <c r="C566" t="s">
         <v>872</v>
       </c>
       <c r="D566" t="s">
-        <v>951</v>
+        <v>2108</v>
       </c>
       <c r="E566" t="s">
-        <v>952</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B567" t="s">
-        <v>168</v>
+        <v>2109</v>
       </c>
       <c r="C567" t="s">
         <v>872</v>
       </c>
       <c r="D567" t="s">
-        <v>953</v>
+        <v>2110</v>
       </c>
       <c r="E567" t="s">
-        <v>954</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B568" t="s">
-        <v>188</v>
+        <v>2111</v>
       </c>
       <c r="C568" t="s">
         <v>872</v>
       </c>
       <c r="D568" t="s">
-        <v>972</v>
+        <v>2112</v>
       </c>
       <c r="E568" t="s">
-        <v>973</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B569" t="s">
-        <v>189</v>
+        <v>2113</v>
       </c>
       <c r="C569" t="s">
         <v>872</v>
       </c>
       <c r="D569" t="s">
-        <v>974</v>
+        <v>2114</v>
       </c>
       <c r="E569" t="s">
-        <v>975</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B570" t="s">
-        <v>597</v>
+        <v>2115</v>
       </c>
       <c r="C570" t="s">
-        <v>595</v>
+        <v>872</v>
       </c>
       <c r="D570" t="s">
-        <v>598</v>
+        <v>2116</v>
       </c>
       <c r="E570" t="s">
-        <v>597</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>1767</v>
+        <v>149</v>
       </c>
       <c r="B571" t="s">
-        <v>129</v>
+        <v>2117</v>
       </c>
       <c r="C571" t="s">
-        <v>772</v>
+        <v>872</v>
       </c>
       <c r="D571" t="s">
-        <v>868</v>
+        <v>2118</v>
       </c>
       <c r="E571" t="s">
-        <v>869</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B572" t="s">
-        <v>130</v>
+        <v>2119</v>
       </c>
       <c r="C572" t="s">
-        <v>772</v>
+        <v>872</v>
       </c>
       <c r="D572" t="s">
-        <v>870</v>
+        <v>2120</v>
       </c>
       <c r="E572" t="s">
-        <v>871</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B573" t="s">
-        <v>131</v>
+        <v>2121</v>
       </c>
       <c r="C573" t="s">
         <v>872</v>
       </c>
       <c r="D573" t="s">
-        <v>873</v>
+        <v>2149</v>
       </c>
       <c r="E573" t="s">
-        <v>874</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B574" t="s">
-        <v>132</v>
+        <v>2122</v>
       </c>
       <c r="C574" t="s">
         <v>872</v>
       </c>
       <c r="D574" t="s">
-        <v>875</v>
+        <v>2123</v>
       </c>
       <c r="E574" t="s">
-        <v>876</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B575" t="s">
-        <v>133</v>
+        <v>594</v>
       </c>
       <c r="C575" t="s">
-        <v>772</v>
+        <v>595</v>
       </c>
       <c r="D575" t="s">
-        <v>877</v>
+        <v>596</v>
       </c>
       <c r="E575" t="s">
-        <v>878</v>
+        <v>594</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B576" t="s">
-        <v>134</v>
+        <v>594</v>
       </c>
       <c r="C576" t="s">
-        <v>772</v>
+        <v>595</v>
       </c>
       <c r="D576" t="s">
-        <v>879</v>
+        <v>596</v>
       </c>
       <c r="E576" t="s">
-        <v>880</v>
+        <v>594</v>
       </c>
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B577" t="s">
-        <v>135</v>
+        <v>2067</v>
       </c>
       <c r="C577" t="s">
         <v>872</v>
       </c>
       <c r="D577" t="s">
-        <v>881</v>
+        <v>916</v>
       </c>
       <c r="E577" t="s">
-        <v>882</v>
+        <v>917</v>
       </c>
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B578" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="C578" t="s">
-        <v>772</v>
+        <v>872</v>
       </c>
       <c r="D578" t="s">
-        <v>883</v>
+        <v>931</v>
       </c>
       <c r="E578" t="s">
-        <v>884</v>
+        <v>932</v>
       </c>
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B579" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="C579" t="s">
-        <v>772</v>
+        <v>872</v>
       </c>
       <c r="D579" t="s">
-        <v>885</v>
+        <v>921</v>
       </c>
       <c r="E579" t="s">
-        <v>886</v>
+        <v>922</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B580" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="C580" t="s">
         <v>872</v>
       </c>
       <c r="D580" t="s">
-        <v>887</v>
+        <v>923</v>
       </c>
       <c r="E580" t="s">
-        <v>888</v>
+        <v>924</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B581" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="C581" t="s">
-        <v>772</v>
+        <v>872</v>
       </c>
       <c r="D581" t="s">
-        <v>889</v>
+        <v>925</v>
       </c>
       <c r="E581" t="s">
-        <v>890</v>
+        <v>926</v>
       </c>
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B582" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="C582" t="s">
-        <v>772</v>
+        <v>872</v>
       </c>
       <c r="D582" t="s">
-        <v>891</v>
+        <v>2066</v>
       </c>
       <c r="E582" t="s">
-        <v>892</v>
+        <v>928</v>
       </c>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B583" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="C583" t="s">
         <v>872</v>
       </c>
       <c r="D583" t="s">
-        <v>893</v>
+        <v>929</v>
       </c>
       <c r="E583" t="s">
-        <v>894</v>
+        <v>930</v>
       </c>
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B584" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="C584" t="s">
         <v>872</v>
       </c>
       <c r="D584" t="s">
-        <v>895</v>
+        <v>935</v>
       </c>
       <c r="E584" t="s">
-        <v>896</v>
+        <v>936</v>
       </c>
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B585" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C585" t="s">
         <v>872</v>
       </c>
       <c r="D585" t="s">
-        <v>897</v>
+        <v>937</v>
       </c>
       <c r="E585" t="s">
-        <v>898</v>
+        <v>938</v>
       </c>
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B586" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="C586" t="s">
-        <v>705</v>
+        <v>872</v>
       </c>
       <c r="D586" t="s">
-        <v>1828</v>
+        <v>939</v>
       </c>
       <c r="E586" t="s">
-        <v>1829</v>
+        <v>940</v>
       </c>
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B587" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="C587" t="s">
         <v>872</v>
       </c>
       <c r="D587" t="s">
-        <v>899</v>
+        <v>941</v>
       </c>
       <c r="E587" t="s">
-        <v>900</v>
+        <v>942</v>
       </c>
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B588" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="C588" t="s">
         <v>872</v>
       </c>
       <c r="D588" t="s">
-        <v>901</v>
+        <v>945</v>
       </c>
       <c r="E588" t="s">
-        <v>902</v>
+        <v>946</v>
       </c>
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B589" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C589" t="s">
         <v>872</v>
       </c>
       <c r="D589" t="s">
-        <v>903</v>
+        <v>947</v>
       </c>
       <c r="E589" t="s">
-        <v>904</v>
+        <v>948</v>
       </c>
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B590" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C590" t="s">
         <v>872</v>
       </c>
       <c r="D590" t="s">
-        <v>905</v>
+        <v>949</v>
       </c>
       <c r="E590" t="s">
-        <v>906</v>
+        <v>950</v>
       </c>
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>1767</v>
+        <v>190</v>
       </c>
       <c r="B591" t="s">
-        <v>1768</v>
+        <v>167</v>
+      </c>
+      <c r="C591" t="s">
+        <v>872</v>
       </c>
       <c r="D591" t="s">
-        <v>1769</v>
+        <v>951</v>
       </c>
       <c r="E591" t="s">
-        <v>1771</v>
+        <v>952</v>
       </c>
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B592" t="s">
-        <v>1772</v>
+        <v>168</v>
       </c>
       <c r="C592" t="s">
-        <v>772</v>
+        <v>872</v>
       </c>
       <c r="D592" t="s">
-        <v>1782</v>
+        <v>953</v>
       </c>
       <c r="E592" t="s">
-        <v>1783</v>
+        <v>954</v>
       </c>
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B593" t="s">
-        <v>1773</v>
+        <v>188</v>
       </c>
       <c r="C593" t="s">
-        <v>595</v>
+        <v>872</v>
       </c>
       <c r="D593" t="s">
-        <v>1784</v>
+        <v>972</v>
       </c>
       <c r="E593" t="s">
-        <v>1785</v>
+        <v>973</v>
       </c>
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="B594" t="s">
-        <v>1774</v>
+        <v>189</v>
       </c>
       <c r="C594" t="s">
         <v>872</v>
       </c>
       <c r="D594" t="s">
-        <v>1786</v>
+        <v>974</v>
       </c>
       <c r="E594" t="s">
-        <v>1787</v>
+        <v>975</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
@@ -22989,33 +23740,33 @@
         <v>128</v>
       </c>
       <c r="B595" t="s">
-        <v>1775</v>
+        <v>597</v>
       </c>
       <c r="C595" t="s">
-        <v>772</v>
+        <v>595</v>
       </c>
       <c r="D595" t="s">
-        <v>1788</v>
+        <v>598</v>
       </c>
       <c r="E595" t="s">
-        <v>1789</v>
+        <v>597</v>
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>128</v>
+        <v>1767</v>
       </c>
       <c r="B596" t="s">
-        <v>1776</v>
+        <v>129</v>
       </c>
       <c r="C596" t="s">
-        <v>595</v>
+        <v>772</v>
       </c>
       <c r="D596" t="s">
-        <v>1790</v>
+        <v>868</v>
       </c>
       <c r="E596" t="s">
-        <v>1791</v>
+        <v>869</v>
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
@@ -23023,16 +23774,16 @@
         <v>128</v>
       </c>
       <c r="B597" t="s">
-        <v>1777</v>
+        <v>130</v>
       </c>
       <c r="C597" t="s">
-        <v>872</v>
+        <v>772</v>
       </c>
       <c r="D597" t="s">
-        <v>1792</v>
+        <v>870</v>
       </c>
       <c r="E597" t="s">
-        <v>1793</v>
+        <v>871</v>
       </c>
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.25">
@@ -23040,16 +23791,16 @@
         <v>128</v>
       </c>
       <c r="B598" t="s">
-        <v>1778</v>
+        <v>131</v>
       </c>
       <c r="C598" t="s">
-        <v>608</v>
+        <v>872</v>
       </c>
       <c r="D598" t="s">
-        <v>1794</v>
+        <v>873</v>
       </c>
       <c r="E598" t="s">
-        <v>1795</v>
+        <v>874</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
@@ -23057,16 +23808,16 @@
         <v>128</v>
       </c>
       <c r="B599" t="s">
-        <v>1779</v>
+        <v>132</v>
       </c>
       <c r="C599" t="s">
-        <v>608</v>
+        <v>872</v>
       </c>
       <c r="D599" t="s">
-        <v>1796</v>
+        <v>875</v>
       </c>
       <c r="E599" t="s">
-        <v>1797</v>
+        <v>876</v>
       </c>
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.25">
@@ -23074,16 +23825,16 @@
         <v>128</v>
       </c>
       <c r="B600" t="s">
-        <v>1780</v>
+        <v>133</v>
       </c>
       <c r="C600" t="s">
-        <v>608</v>
+        <v>772</v>
       </c>
       <c r="D600" t="s">
-        <v>1798</v>
+        <v>877</v>
       </c>
       <c r="E600" t="s">
-        <v>1799</v>
+        <v>878</v>
       </c>
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.25">
@@ -23091,1189 +23842,1186 @@
         <v>128</v>
       </c>
       <c r="B601" t="s">
-        <v>1781</v>
+        <v>134</v>
       </c>
       <c r="C601" t="s">
-        <v>1800</v>
+        <v>772</v>
       </c>
       <c r="D601" t="s">
-        <v>1801</v>
+        <v>879</v>
       </c>
       <c r="E601" t="s">
-        <v>1802</v>
+        <v>880</v>
       </c>
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B602" t="s">
-        <v>599</v>
+        <v>135</v>
       </c>
       <c r="C602" t="s">
-        <v>595</v>
+        <v>872</v>
       </c>
       <c r="D602" t="s">
-        <v>600</v>
+        <v>881</v>
       </c>
       <c r="E602" t="s">
-        <v>599</v>
+        <v>882</v>
       </c>
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B603" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="C603" t="s">
-        <v>705</v>
+        <v>772</v>
       </c>
       <c r="D603" t="s">
-        <v>828</v>
+        <v>883</v>
       </c>
       <c r="E603" t="s">
-        <v>829</v>
+        <v>884</v>
       </c>
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B604" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="C604" t="s">
-        <v>705</v>
+        <v>772</v>
       </c>
       <c r="D604" t="s">
-        <v>830</v>
+        <v>885</v>
       </c>
       <c r="E604" t="s">
-        <v>831</v>
+        <v>886</v>
       </c>
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B605" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="C605" t="s">
-        <v>705</v>
+        <v>872</v>
       </c>
       <c r="D605" t="s">
-        <v>832</v>
+        <v>887</v>
       </c>
       <c r="E605" t="s">
-        <v>833</v>
+        <v>888</v>
       </c>
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B606" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="C606" t="s">
-        <v>677</v>
+        <v>772</v>
       </c>
       <c r="D606" t="s">
-        <v>834</v>
+        <v>889</v>
       </c>
       <c r="E606" t="s">
-        <v>835</v>
+        <v>890</v>
       </c>
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B607" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="C607" t="s">
-        <v>672</v>
+        <v>772</v>
       </c>
       <c r="D607" t="s">
-        <v>836</v>
+        <v>891</v>
       </c>
       <c r="E607" t="s">
-        <v>837</v>
+        <v>892</v>
       </c>
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B608" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="C608" t="s">
-        <v>705</v>
+        <v>872</v>
       </c>
       <c r="D608" t="s">
-        <v>838</v>
+        <v>893</v>
       </c>
       <c r="E608" t="s">
-        <v>839</v>
+        <v>894</v>
       </c>
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B609" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="C609" t="s">
-        <v>677</v>
+        <v>872</v>
       </c>
       <c r="D609" t="s">
-        <v>840</v>
+        <v>895</v>
       </c>
       <c r="E609" t="s">
-        <v>841</v>
+        <v>896</v>
       </c>
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B610" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="C610" t="s">
-        <v>672</v>
+        <v>872</v>
       </c>
       <c r="D610" t="s">
-        <v>842</v>
+        <v>897</v>
       </c>
       <c r="E610" t="s">
-        <v>843</v>
+        <v>898</v>
       </c>
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B611" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="C611" t="s">
         <v>705</v>
       </c>
       <c r="D611" t="s">
-        <v>844</v>
+        <v>1828</v>
       </c>
       <c r="E611" t="s">
-        <v>845</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B612" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="C612" t="s">
-        <v>677</v>
+        <v>872</v>
       </c>
       <c r="D612" t="s">
-        <v>846</v>
+        <v>899</v>
       </c>
       <c r="E612" t="s">
-        <v>847</v>
+        <v>900</v>
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B613" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="C613" t="s">
-        <v>672</v>
+        <v>872</v>
       </c>
       <c r="D613" t="s">
-        <v>848</v>
+        <v>901</v>
       </c>
       <c r="E613" t="s">
-        <v>849</v>
+        <v>902</v>
       </c>
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B614" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="C614" t="s">
-        <v>705</v>
+        <v>872</v>
       </c>
       <c r="D614" t="s">
-        <v>850</v>
+        <v>903</v>
       </c>
       <c r="E614" t="s">
-        <v>851</v>
+        <v>904</v>
       </c>
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B615" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="C615" t="s">
-        <v>677</v>
+        <v>872</v>
       </c>
       <c r="D615" t="s">
-        <v>852</v>
+        <v>905</v>
       </c>
       <c r="E615" t="s">
-        <v>853</v>
+        <v>906</v>
       </c>
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>107</v>
+        <v>1767</v>
       </c>
       <c r="B616" t="s">
-        <v>121</v>
-      </c>
-      <c r="C616" t="s">
-        <v>672</v>
+        <v>1768</v>
       </c>
       <c r="D616" t="s">
-        <v>854</v>
+        <v>1769</v>
       </c>
       <c r="E616" t="s">
-        <v>855</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B617" t="s">
-        <v>2065</v>
+        <v>1772</v>
       </c>
       <c r="C617" t="s">
-        <v>705</v>
+        <v>772</v>
       </c>
       <c r="D617" t="s">
-        <v>856</v>
+        <v>1782</v>
       </c>
       <c r="E617" t="s">
-        <v>857</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B618" t="s">
-        <v>123</v>
+        <v>1773</v>
       </c>
       <c r="C618" t="s">
-        <v>677</v>
+        <v>595</v>
       </c>
       <c r="D618" t="s">
-        <v>858</v>
+        <v>1784</v>
       </c>
       <c r="E618" t="s">
-        <v>859</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B619" t="s">
-        <v>124</v>
+        <v>1774</v>
       </c>
       <c r="C619" t="s">
-        <v>672</v>
+        <v>872</v>
       </c>
       <c r="D619" t="s">
-        <v>860</v>
+        <v>1786</v>
       </c>
       <c r="E619" t="s">
-        <v>861</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B620" t="s">
-        <v>125</v>
+        <v>1775</v>
       </c>
       <c r="C620" t="s">
-        <v>705</v>
+        <v>772</v>
       </c>
       <c r="D620" t="s">
-        <v>862</v>
+        <v>1788</v>
       </c>
       <c r="E620" t="s">
-        <v>863</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B621" t="s">
-        <v>126</v>
+        <v>1776</v>
       </c>
       <c r="C621" t="s">
-        <v>677</v>
+        <v>595</v>
       </c>
       <c r="D621" t="s">
-        <v>864</v>
+        <v>1790</v>
       </c>
       <c r="E621" t="s">
-        <v>865</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B622" t="s">
-        <v>127</v>
+        <v>1777</v>
       </c>
       <c r="C622" t="s">
-        <v>672</v>
+        <v>872</v>
       </c>
       <c r="D622" t="s">
-        <v>866</v>
+        <v>1792</v>
       </c>
       <c r="E622" t="s">
-        <v>867</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="B623" t="s">
-        <v>1743</v>
+        <v>1778</v>
       </c>
       <c r="C623" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="D623" t="s">
-        <v>1746</v>
+        <v>1794</v>
       </c>
       <c r="E623" t="s">
-        <v>1752</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="B624" t="s">
-        <v>1744</v>
+        <v>1779</v>
       </c>
       <c r="C624" t="s">
-        <v>1745</v>
+        <v>608</v>
       </c>
       <c r="D624" t="s">
-        <v>1747</v>
+        <v>1796</v>
       </c>
       <c r="E624" t="s">
-        <v>1753</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="B625" t="s">
-        <v>1748</v>
+        <v>1780</v>
       </c>
       <c r="C625" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="D625" t="s">
-        <v>1750</v>
+        <v>1798</v>
       </c>
       <c r="E625" t="s">
-        <v>605</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="B626" t="s">
-        <v>1749</v>
+        <v>1781</v>
       </c>
       <c r="C626" t="s">
-        <v>606</v>
+        <v>1800</v>
       </c>
       <c r="D626" t="s">
-        <v>1751</v>
+        <v>1801</v>
       </c>
       <c r="E626" t="s">
-        <v>607</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B627" t="s">
-        <v>1754</v>
+        <v>599</v>
       </c>
       <c r="C627" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="D627" t="s">
-        <v>1756</v>
+        <v>600</v>
       </c>
       <c r="E627" t="s">
-        <v>1758</v>
+        <v>599</v>
       </c>
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B628" t="s">
-        <v>1755</v>
+        <v>108</v>
       </c>
       <c r="C628" t="s">
-        <v>1760</v>
+        <v>705</v>
       </c>
       <c r="D628" t="s">
-        <v>1757</v>
+        <v>828</v>
       </c>
       <c r="E628" t="s">
-        <v>1759</v>
+        <v>829</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B629" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="C629" t="s">
-        <v>608</v>
+        <v>705</v>
       </c>
       <c r="D629" t="s">
-        <v>609</v>
+        <v>830</v>
       </c>
       <c r="E629" t="s">
-        <v>610</v>
+        <v>831</v>
       </c>
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B630" t="s">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="C630" t="s">
-        <v>608</v>
+        <v>705</v>
       </c>
       <c r="D630" t="s">
-        <v>611</v>
+        <v>832</v>
       </c>
       <c r="E630" t="s">
-        <v>612</v>
+        <v>833</v>
       </c>
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B631" t="s">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="C631" t="s">
-        <v>613</v>
+        <v>677</v>
       </c>
       <c r="D631" t="s">
-        <v>614</v>
+        <v>834</v>
       </c>
       <c r="E631" t="s">
-        <v>615</v>
+        <v>835</v>
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B632" t="s">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="C632" t="s">
-        <v>608</v>
+        <v>672</v>
       </c>
       <c r="D632" t="s">
-        <v>616</v>
+        <v>836</v>
       </c>
       <c r="E632" t="s">
-        <v>617</v>
+        <v>837</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B633" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="C633" t="s">
-        <v>608</v>
+        <v>705</v>
       </c>
       <c r="D633" t="s">
-        <v>618</v>
+        <v>838</v>
       </c>
       <c r="E633" t="s">
-        <v>619</v>
+        <v>839</v>
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B634" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="C634" t="s">
-        <v>608</v>
+        <v>677</v>
       </c>
       <c r="D634" t="s">
-        <v>620</v>
+        <v>840</v>
       </c>
       <c r="E634" t="s">
-        <v>621</v>
+        <v>841</v>
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B635" t="s">
-        <v>11</v>
+        <v>115</v>
       </c>
       <c r="C635" t="s">
-        <v>608</v>
+        <v>672</v>
       </c>
       <c r="D635" t="s">
-        <v>622</v>
+        <v>842</v>
       </c>
       <c r="E635" t="s">
-        <v>623</v>
+        <v>843</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B636" t="s">
-        <v>12</v>
+        <v>116</v>
       </c>
       <c r="C636" t="s">
-        <v>608</v>
+        <v>705</v>
       </c>
       <c r="D636" t="s">
-        <v>624</v>
+        <v>844</v>
       </c>
       <c r="E636" t="s">
-        <v>625</v>
+        <v>845</v>
       </c>
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B637" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="C637" t="s">
-        <v>608</v>
+        <v>677</v>
       </c>
       <c r="D637" t="s">
-        <v>626</v>
+        <v>846</v>
       </c>
       <c r="E637" t="s">
-        <v>627</v>
+        <v>847</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B638" t="s">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="C638" t="s">
-        <v>608</v>
+        <v>672</v>
       </c>
       <c r="D638" t="s">
-        <v>628</v>
+        <v>848</v>
       </c>
       <c r="E638" t="s">
-        <v>629</v>
+        <v>849</v>
       </c>
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B639" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="C639" t="s">
-        <v>608</v>
+        <v>705</v>
       </c>
       <c r="D639" t="s">
-        <v>630</v>
+        <v>850</v>
       </c>
       <c r="E639" t="s">
-        <v>631</v>
+        <v>851</v>
       </c>
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B640" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="C640" t="s">
-        <v>608</v>
+        <v>677</v>
       </c>
       <c r="D640" t="s">
-        <v>632</v>
+        <v>852</v>
       </c>
       <c r="E640" t="s">
-        <v>633</v>
+        <v>853</v>
       </c>
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B641" t="s">
-        <v>17</v>
+        <v>121</v>
       </c>
       <c r="C641" t="s">
-        <v>608</v>
+        <v>672</v>
       </c>
       <c r="D641" t="s">
-        <v>634</v>
+        <v>854</v>
       </c>
       <c r="E641" t="s">
-        <v>635</v>
+        <v>855</v>
       </c>
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B642" t="s">
-        <v>18</v>
+        <v>2065</v>
       </c>
       <c r="C642" t="s">
-        <v>608</v>
+        <v>705</v>
       </c>
       <c r="D642" t="s">
-        <v>636</v>
+        <v>856</v>
       </c>
       <c r="E642" t="s">
-        <v>637</v>
+        <v>857</v>
       </c>
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B643" t="s">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="C643" t="s">
-        <v>638</v>
+        <v>677</v>
       </c>
       <c r="D643" t="s">
-        <v>639</v>
+        <v>858</v>
       </c>
       <c r="E643" t="s">
-        <v>640</v>
+        <v>859</v>
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B644" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="C644" t="s">
-        <v>638</v>
+        <v>672</v>
       </c>
       <c r="D644" t="s">
-        <v>641</v>
+        <v>860</v>
       </c>
       <c r="E644" t="s">
-        <v>642</v>
+        <v>861</v>
       </c>
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B645" t="s">
-        <v>1804</v>
+        <v>125</v>
       </c>
       <c r="C645" t="s">
-        <v>608</v>
+        <v>705</v>
       </c>
       <c r="D645" t="s">
-        <v>1805</v>
+        <v>862</v>
       </c>
       <c r="E645" t="s">
-        <v>1806</v>
+        <v>863</v>
       </c>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="B646" t="s">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="C646" t="s">
-        <v>601</v>
+        <v>677</v>
       </c>
       <c r="D646" t="s">
-        <v>602</v>
+        <v>864</v>
       </c>
       <c r="E646" t="s">
-        <v>603</v>
+        <v>865</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="B647" t="s">
-        <v>21</v>
+        <v>127</v>
       </c>
       <c r="C647" t="s">
-        <v>643</v>
+        <v>672</v>
       </c>
       <c r="D647" t="s">
-        <v>644</v>
+        <v>866</v>
       </c>
       <c r="E647" t="s">
-        <v>645</v>
+        <v>867</v>
       </c>
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B648" t="s">
-        <v>22</v>
+        <v>1743</v>
       </c>
       <c r="C648" t="s">
-        <v>643</v>
+        <v>601</v>
       </c>
       <c r="D648" t="s">
-        <v>646</v>
+        <v>1746</v>
       </c>
       <c r="E648" t="s">
-        <v>647</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B649" t="s">
-        <v>23</v>
+        <v>1744</v>
       </c>
       <c r="C649" t="s">
-        <v>643</v>
+        <v>1745</v>
       </c>
       <c r="D649" t="s">
-        <v>648</v>
+        <v>1747</v>
       </c>
       <c r="E649" t="s">
-        <v>649</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B650" t="s">
-        <v>24</v>
+        <v>1748</v>
       </c>
       <c r="C650" t="s">
-        <v>643</v>
+        <v>604</v>
       </c>
       <c r="D650" t="s">
-        <v>650</v>
+        <v>1750</v>
       </c>
       <c r="E650" t="s">
-        <v>651</v>
+        <v>605</v>
       </c>
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B651" t="s">
-        <v>25</v>
+        <v>1749</v>
       </c>
       <c r="C651" t="s">
-        <v>652</v>
+        <v>606</v>
       </c>
       <c r="D651" t="s">
-        <v>653</v>
+        <v>1751</v>
       </c>
       <c r="E651" t="s">
-        <v>654</v>
+        <v>607</v>
       </c>
     </row>
     <row r="652" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B652" t="s">
-        <v>26</v>
+        <v>1754</v>
       </c>
       <c r="C652" t="s">
-        <v>655</v>
+        <v>604</v>
       </c>
       <c r="D652" t="s">
-        <v>656</v>
+        <v>1756</v>
       </c>
       <c r="E652" t="s">
-        <v>657</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B653" t="s">
-        <v>27</v>
+        <v>1755</v>
       </c>
       <c r="C653" t="s">
-        <v>658</v>
+        <v>1760</v>
       </c>
       <c r="D653" t="s">
-        <v>659</v>
+        <v>1757</v>
       </c>
       <c r="E653" t="s">
-        <v>660</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B654" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="C654" t="s">
-        <v>661</v>
+        <v>608</v>
       </c>
       <c r="D654" t="s">
-        <v>662</v>
+        <v>609</v>
       </c>
       <c r="E654" t="s">
-        <v>663</v>
+        <v>610</v>
       </c>
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B655" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C655" t="s">
-        <v>643</v>
+        <v>608</v>
       </c>
       <c r="D655" t="s">
-        <v>664</v>
+        <v>611</v>
       </c>
       <c r="E655" t="s">
-        <v>665</v>
+        <v>612</v>
       </c>
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B656" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C656" t="s">
-        <v>643</v>
+        <v>613</v>
       </c>
       <c r="D656" t="s">
-        <v>666</v>
+        <v>614</v>
       </c>
       <c r="E656" t="s">
-        <v>667</v>
+        <v>615</v>
       </c>
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B657" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C657" t="s">
-        <v>643</v>
+        <v>608</v>
       </c>
       <c r="D657" t="s">
-        <v>668</v>
+        <v>616</v>
       </c>
       <c r="E657" t="s">
-        <v>669</v>
+        <v>617</v>
       </c>
     </row>
     <row r="658" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B658" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C658" t="s">
-        <v>643</v>
+        <v>608</v>
       </c>
       <c r="D658" t="s">
-        <v>670</v>
+        <v>618</v>
       </c>
       <c r="E658" t="s">
-        <v>671</v>
+        <v>619</v>
       </c>
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B659" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C659" t="s">
-        <v>672</v>
+        <v>608</v>
       </c>
       <c r="D659" t="s">
-        <v>673</v>
+        <v>620</v>
       </c>
       <c r="E659" t="s">
-        <v>674</v>
+        <v>621</v>
       </c>
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B660" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C660" t="s">
-        <v>643</v>
+        <v>608</v>
       </c>
       <c r="D660" t="s">
-        <v>675</v>
+        <v>622</v>
       </c>
       <c r="E660" t="s">
-        <v>676</v>
+        <v>623</v>
       </c>
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B661" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C661" t="s">
-        <v>677</v>
+        <v>608</v>
       </c>
       <c r="D661" t="s">
-        <v>678</v>
+        <v>624</v>
       </c>
       <c r="E661" t="s">
-        <v>679</v>
+        <v>625</v>
       </c>
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B662" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C662" t="s">
-        <v>655</v>
+        <v>608</v>
       </c>
       <c r="D662" t="s">
-        <v>680</v>
+        <v>626</v>
       </c>
       <c r="E662" t="s">
-        <v>681</v>
+        <v>627</v>
       </c>
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B663" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C663" t="s">
-        <v>652</v>
+        <v>608</v>
       </c>
       <c r="D663" t="s">
-        <v>682</v>
+        <v>628</v>
       </c>
       <c r="E663" t="s">
-        <v>683</v>
+        <v>629</v>
       </c>
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B664" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C664" t="s">
-        <v>684</v>
+        <v>608</v>
       </c>
       <c r="D664" t="s">
-        <v>685</v>
+        <v>630</v>
       </c>
       <c r="E664" t="s">
-        <v>686</v>
+        <v>631</v>
       </c>
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B665" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C665" t="s">
-        <v>672</v>
+        <v>608</v>
       </c>
       <c r="D665" t="s">
-        <v>687</v>
+        <v>632</v>
       </c>
       <c r="E665" t="s">
-        <v>688</v>
+        <v>633</v>
       </c>
     </row>
     <row r="666" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B666" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C666" t="s">
-        <v>672</v>
+        <v>608</v>
       </c>
       <c r="D666" t="s">
-        <v>689</v>
+        <v>634</v>
       </c>
       <c r="E666" t="s">
-        <v>690</v>
+        <v>635</v>
       </c>
     </row>
     <row r="667" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B667" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="C667" t="s">
-        <v>672</v>
+        <v>608</v>
       </c>
       <c r="D667" t="s">
-        <v>691</v>
+        <v>636</v>
       </c>
       <c r="E667" t="s">
-        <v>692</v>
+        <v>637</v>
       </c>
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B668" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="C668" t="s">
-        <v>672</v>
+        <v>638</v>
       </c>
       <c r="D668" t="s">
-        <v>693</v>
+        <v>639</v>
       </c>
       <c r="E668" t="s">
-        <v>694</v>
+        <v>640</v>
       </c>
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B669" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="C669" t="s">
-        <v>695</v>
+        <v>638</v>
       </c>
       <c r="D669" t="s">
-        <v>696</v>
+        <v>641</v>
       </c>
       <c r="E669" t="s">
-        <v>697</v>
+        <v>642</v>
       </c>
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B670" t="s">
-        <v>44</v>
+        <v>1804</v>
       </c>
       <c r="C670" t="s">
-        <v>698</v>
+        <v>608</v>
       </c>
       <c r="D670" t="s">
-        <v>699</v>
+        <v>1805</v>
       </c>
       <c r="E670" t="s">
-        <v>700</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
@@ -24281,16 +25029,16 @@
         <v>2</v>
       </c>
       <c r="B671" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="C671" t="s">
-        <v>698</v>
+        <v>601</v>
       </c>
       <c r="D671" t="s">
-        <v>701</v>
+        <v>602</v>
       </c>
       <c r="E671" t="s">
-        <v>702</v>
+        <v>603</v>
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
@@ -24298,20 +25046,445 @@
         <v>2</v>
       </c>
       <c r="B672" t="s">
+        <v>21</v>
+      </c>
+      <c r="C672" t="s">
+        <v>643</v>
+      </c>
+      <c r="D672" t="s">
+        <v>644</v>
+      </c>
+      <c r="E672" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="673" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A673" t="s">
+        <v>2</v>
+      </c>
+      <c r="B673" t="s">
+        <v>22</v>
+      </c>
+      <c r="C673" t="s">
+        <v>643</v>
+      </c>
+      <c r="D673" t="s">
+        <v>646</v>
+      </c>
+      <c r="E673" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="674" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A674" t="s">
+        <v>2</v>
+      </c>
+      <c r="B674" t="s">
+        <v>23</v>
+      </c>
+      <c r="C674" t="s">
+        <v>643</v>
+      </c>
+      <c r="D674" t="s">
+        <v>648</v>
+      </c>
+      <c r="E674" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="675" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A675" t="s">
+        <v>2</v>
+      </c>
+      <c r="B675" t="s">
+        <v>24</v>
+      </c>
+      <c r="C675" t="s">
+        <v>643</v>
+      </c>
+      <c r="D675" t="s">
+        <v>650</v>
+      </c>
+      <c r="E675" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="676" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A676" t="s">
+        <v>2</v>
+      </c>
+      <c r="B676" t="s">
+        <v>25</v>
+      </c>
+      <c r="C676" t="s">
+        <v>652</v>
+      </c>
+      <c r="D676" t="s">
+        <v>653</v>
+      </c>
+      <c r="E676" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="677" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A677" t="s">
+        <v>2</v>
+      </c>
+      <c r="B677" t="s">
+        <v>26</v>
+      </c>
+      <c r="C677" t="s">
+        <v>655</v>
+      </c>
+      <c r="D677" t="s">
+        <v>656</v>
+      </c>
+      <c r="E677" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="678" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A678" t="s">
+        <v>2</v>
+      </c>
+      <c r="B678" t="s">
+        <v>27</v>
+      </c>
+      <c r="C678" t="s">
+        <v>658</v>
+      </c>
+      <c r="D678" t="s">
+        <v>659</v>
+      </c>
+      <c r="E678" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="679" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A679" t="s">
+        <v>2</v>
+      </c>
+      <c r="B679" t="s">
+        <v>28</v>
+      </c>
+      <c r="C679" t="s">
+        <v>661</v>
+      </c>
+      <c r="D679" t="s">
+        <v>662</v>
+      </c>
+      <c r="E679" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="680" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A680" t="s">
+        <v>2</v>
+      </c>
+      <c r="B680" t="s">
+        <v>29</v>
+      </c>
+      <c r="C680" t="s">
+        <v>643</v>
+      </c>
+      <c r="D680" t="s">
+        <v>664</v>
+      </c>
+      <c r="E680" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="681" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A681" t="s">
+        <v>2</v>
+      </c>
+      <c r="B681" t="s">
+        <v>30</v>
+      </c>
+      <c r="C681" t="s">
+        <v>643</v>
+      </c>
+      <c r="D681" t="s">
+        <v>666</v>
+      </c>
+      <c r="E681" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="682" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A682" t="s">
+        <v>2</v>
+      </c>
+      <c r="B682" t="s">
+        <v>31</v>
+      </c>
+      <c r="C682" t="s">
+        <v>643</v>
+      </c>
+      <c r="D682" t="s">
+        <v>668</v>
+      </c>
+      <c r="E682" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="683" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A683" t="s">
+        <v>2</v>
+      </c>
+      <c r="B683" t="s">
+        <v>32</v>
+      </c>
+      <c r="C683" t="s">
+        <v>643</v>
+      </c>
+      <c r="D683" t="s">
+        <v>670</v>
+      </c>
+      <c r="E683" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="684" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A684" t="s">
+        <v>2</v>
+      </c>
+      <c r="B684" t="s">
+        <v>33</v>
+      </c>
+      <c r="C684" t="s">
+        <v>672</v>
+      </c>
+      <c r="D684" t="s">
+        <v>673</v>
+      </c>
+      <c r="E684" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="685" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A685" t="s">
+        <v>2</v>
+      </c>
+      <c r="B685" t="s">
+        <v>34</v>
+      </c>
+      <c r="C685" t="s">
+        <v>643</v>
+      </c>
+      <c r="D685" t="s">
+        <v>675</v>
+      </c>
+      <c r="E685" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="686" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A686" t="s">
+        <v>2</v>
+      </c>
+      <c r="B686" t="s">
+        <v>35</v>
+      </c>
+      <c r="C686" t="s">
+        <v>677</v>
+      </c>
+      <c r="D686" t="s">
+        <v>678</v>
+      </c>
+      <c r="E686" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="687" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A687" t="s">
+        <v>2</v>
+      </c>
+      <c r="B687" t="s">
+        <v>36</v>
+      </c>
+      <c r="C687" t="s">
+        <v>655</v>
+      </c>
+      <c r="D687" t="s">
+        <v>680</v>
+      </c>
+      <c r="E687" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="688" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A688" t="s">
+        <v>2</v>
+      </c>
+      <c r="B688" t="s">
+        <v>37</v>
+      </c>
+      <c r="C688" t="s">
+        <v>652</v>
+      </c>
+      <c r="D688" t="s">
+        <v>682</v>
+      </c>
+      <c r="E688" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="689" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A689" t="s">
+        <v>2</v>
+      </c>
+      <c r="B689" t="s">
+        <v>38</v>
+      </c>
+      <c r="C689" t="s">
+        <v>684</v>
+      </c>
+      <c r="D689" t="s">
+        <v>685</v>
+      </c>
+      <c r="E689" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="690" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A690" t="s">
+        <v>2</v>
+      </c>
+      <c r="B690" t="s">
+        <v>39</v>
+      </c>
+      <c r="C690" t="s">
+        <v>672</v>
+      </c>
+      <c r="D690" t="s">
+        <v>687</v>
+      </c>
+      <c r="E690" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="691" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A691" t="s">
+        <v>2</v>
+      </c>
+      <c r="B691" t="s">
+        <v>40</v>
+      </c>
+      <c r="C691" t="s">
+        <v>672</v>
+      </c>
+      <c r="D691" t="s">
+        <v>689</v>
+      </c>
+      <c r="E691" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="692" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A692" t="s">
+        <v>2</v>
+      </c>
+      <c r="B692" t="s">
+        <v>41</v>
+      </c>
+      <c r="C692" t="s">
+        <v>672</v>
+      </c>
+      <c r="D692" t="s">
+        <v>691</v>
+      </c>
+      <c r="E692" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="693" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A693" t="s">
+        <v>2</v>
+      </c>
+      <c r="B693" t="s">
+        <v>42</v>
+      </c>
+      <c r="C693" t="s">
+        <v>672</v>
+      </c>
+      <c r="D693" t="s">
+        <v>693</v>
+      </c>
+      <c r="E693" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="694" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A694" t="s">
+        <v>2</v>
+      </c>
+      <c r="B694" t="s">
+        <v>43</v>
+      </c>
+      <c r="C694" t="s">
+        <v>695</v>
+      </c>
+      <c r="D694" t="s">
+        <v>696</v>
+      </c>
+      <c r="E694" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="695" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A695" t="s">
+        <v>2</v>
+      </c>
+      <c r="B695" t="s">
+        <v>44</v>
+      </c>
+      <c r="C695" t="s">
+        <v>698</v>
+      </c>
+      <c r="D695" t="s">
+        <v>699</v>
+      </c>
+      <c r="E695" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="696" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A696" t="s">
+        <v>2</v>
+      </c>
+      <c r="B696" t="s">
+        <v>45</v>
+      </c>
+      <c r="C696" t="s">
+        <v>698</v>
+      </c>
+      <c r="D696" t="s">
+        <v>701</v>
+      </c>
+      <c r="E696" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="697" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A697" t="s">
+        <v>2</v>
+      </c>
+      <c r="B697" t="s">
         <v>46</v>
       </c>
-      <c r="C672" t="s">
+      <c r="C697" t="s">
         <v>698</v>
       </c>
-      <c r="D672" t="s">
+      <c r="D697" t="s">
         <v>703</v>
       </c>
-      <c r="E672" t="s">
+      <c r="E697" t="s">
         <v>704</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E702">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E727">
     <sortCondition ref="A1"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
